--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487767_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487767_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5857</v>
+        <v>1.4048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5079</v>
+        <v>2.593</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0779</v>
+        <v>-1.1882</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0959</v>
+        <v>-0.9052</v>
       </c>
       <c r="H2" t="n">
-        <v>0.921</v>
+        <v>2.4903</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1748</v>
+        <v>-3.3955</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6921</v>
+        <v>2.7364</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9868</v>
+        <v>3.8908</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7054</v>
+        <v>-1.1544</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-3.6415</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0657</v>
+        <v>-1.4005</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4695</v>
+        <v>-2.2411</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.2487</v>
+        <v>2.4974</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8731</v>
+        <v>2.4974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5245</v>
+        <v>-0.8667</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.46</v>
+        <v>-0.7272</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0645</v>
+        <v>-0.1396</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2631</v>
+        <v>0.6793</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3975</v>
+        <v>0.5838</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1344</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3443</v>
+        <v>1.1202</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8848</v>
+        <v>0.424</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5405</v>
+        <v>0.6962</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9052</v>
+        <v>2.0959</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4903</v>
+        <v>0.921</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.3955</v>
+        <v>1.1748</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7364</v>
+        <v>2.6921</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8908</v>
+        <v>1.9868</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1544</v>
+        <v>0.7054</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6415</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4005</v>
+        <v>-1.0657</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.2411</v>
+        <v>0.4695</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4974</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4974</v>
+        <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9272</v>
+        <v>-0.99</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4354</v>
+        <v>-0.5438</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4919</v>
+        <v>-0.4462</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6793</v>
+        <v>1.2631</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5838</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0955</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3199</v>
+        <v>-0.5864</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5508</v>
+        <v>-0.6998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2309</v>
+        <v>0.1135</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4745</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1298</v>
+        <v>-0.1367</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>-0.0871</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0679</v>
+        <v>-0.0496</v>
       </c>
       <c r="V4" t="n">
         <v>0.0248</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8731</v>
+        <v>-1.6269</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2322</v>
+        <v>1.5699</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6409</v>
+        <v>-3.1968</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9686</v>
+        <v>3.4178</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5905</v>
+        <v>-0.0446</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.378</v>
+        <v>3.4624</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7871</v>
+        <v>4.5692</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2922</v>
+        <v>0.6864</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0793</v>
+        <v>3.8829</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7556</v>
+        <v>-1.1514</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2983</v>
+        <v>-0.731</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4573</v>
+        <v>-0.4204</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8827</v>
+        <v>-1.8458</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9786</v>
+        <v>-0.9182</v>
       </c>
       <c r="U5" t="n">
-        <v>0.096</v>
+        <v>-0.9277</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3538</v>
+        <v>-3.4071</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3538</v>
+        <v>-3.4071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1669</v>
+        <v>-1.8974</v>
       </c>
       <c r="E6" t="n">
-        <v>1.118</v>
+        <v>-0.8455</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2849</v>
+        <v>-1.0519</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4178</v>
+        <v>-1.9686</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0446</v>
+        <v>-1.5905</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4624</v>
+        <v>-0.378</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5692</v>
+        <v>0.7871</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6864</v>
+        <v>-0.2922</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8829</v>
+        <v>1.0793</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1514</v>
+        <v>-2.7556</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.731</v>
+        <v>-1.2983</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4204</v>
+        <v>-1.4573</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3858</v>
+        <v>-0.907</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3701</v>
+        <v>-0.5919</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0157</v>
+        <v>-0.3151</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.4071</v>
+        <v>0.3538</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.4071</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8945</v>
+        <v>-2.6567</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3949</v>
+        <v>-0.9011</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2895</v>
+        <v>-1.7556</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6853</v>
+        <v>-1.604</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1684</v>
+        <v>-0.5393</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5169</v>
+        <v>-1.0646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4809</v>
+        <v>0.9272</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6375999999999999</v>
+        <v>0.5712</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1568</v>
+        <v>0.3559</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2044</v>
+        <v>-2.5311</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5308</v>
+        <v>-1.1106</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6737</v>
+        <v>-1.4206</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8959</v>
+        <v>-1.3722</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6864</v>
+        <v>-0.7877</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2094</v>
+        <v>-0.5845</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1051</v>
+        <v>-0.513</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3351</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1902</v>
+        <v>-2.9893</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2878</v>
+        <v>-3.3364</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9024</v>
+        <v>0.3471</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.604</v>
+        <v>-1.7115</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5393</v>
+        <v>-0.077</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0646</v>
+        <v>-1.6345</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9272</v>
+        <v>-0.2131</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5712</v>
+        <v>1.1764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3559</v>
+        <v>-1.3896</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5311</v>
+        <v>-1.4984</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1106</v>
+        <v>-1.2535</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4206</v>
+        <v>-0.2449</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9057</v>
+        <v>-0.9886</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1744</v>
+        <v>-0.4615</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7313</v>
+        <v>-0.5271</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.513</v>
+        <v>1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.513</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5816</v>
+        <v>-4.2391</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7231</v>
+        <v>-0.8909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1416</v>
+        <v>-3.3482</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7115</v>
+        <v>-2.6853</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.077</v>
+        <v>-1.1684</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6345</v>
+        <v>-1.5169</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2131</v>
+        <v>-0.4809</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1764</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3896</v>
+        <v>0.1568</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4984</v>
+        <v>-2.2044</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2535</v>
+        <v>-0.5308</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2449</v>
+        <v>-1.6737</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4568</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5808</v>
+        <v>0.5513</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8482</v>
+        <v>0.4005</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7326</v>
+        <v>0.1507</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>-2.1051</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4599</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7076</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.3081</v>
+        <v>-7.281</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.5482</v>
+        <v>-6.6972</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7599</v>
+        <v>-0.5838</v>
       </c>
       <c r="G10" t="n">
         <v>-6.1049</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3295</v>
+        <v>-0.4786</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.426</v>
+        <v>-0.2498</v>
       </c>
       <c r="V10" t="n">
         <v>-1.072</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.4043</v>
+        <v>-18.7518</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.436499999999999</v>
+        <v>-8.783999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-9.967700000000001</v>
@@ -1279,7 +1279,7 @@
         <v>-9.940300000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.061900000000001</v>
+        <v>-4.0619</v>
       </c>
       <c r="I11" t="n">
         <v>-5.878399999999999</v>
@@ -1288,7 +1288,7 @@
         <v>6.2678</v>
       </c>
       <c r="K11" t="n">
-        <v>4.880099999999999</v>
+        <v>4.880100000000001</v>
       </c>
       <c r="L11" t="n">
         <v>1.387799999999999</v>
@@ -1297,10 +1297,10 @@
         <v>-16.2079</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.9421</v>
+        <v>-8.942100000000002</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.266000000000001</v>
+        <v>-7.266</v>
       </c>
       <c r="P11" t="n">
         <v>2.0813</v>
@@ -1312,16 +1312,16 @@
         <v>15.6088</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.936499999999999</v>
+        <v>-7.2841</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.847900000000001</v>
+        <v>-4.1955</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.0887</v>
+        <v>-3.0889</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.608700000000001</v>
+        <v>-3.6087</v>
       </c>
       <c r="W11" t="n">
         <v>2.6712</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.5689</v>
+        <v>13.5348</v>
       </c>
       <c r="E12" t="n">
-        <v>10.6689</v>
+        <v>11.3118</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>2.2229</v>
       </c>
       <c r="G12" t="n">
         <v>6.4101</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1357</v>
+        <v>0.8302</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.64</v>
+        <v>0.0029</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5044</v>
+        <v>0.8273</v>
       </c>
       <c r="V12" t="n">
         <v>5.2539</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6753</v>
+        <v>2.6992</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7584</v>
+        <v>2.2226</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9169</v>
+        <v>0.4765</v>
       </c>
       <c r="G14" t="n">
         <v>1.5876</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8933</v>
+        <v>0.9171</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1802</v>
+        <v>0.6444</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7131</v>
+        <v>0.2727</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0543</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4985</v>
+        <v>2.4897</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7054</v>
+        <v>1.4911</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7931</v>
+        <v>0.9986</v>
       </c>
       <c r="G15" t="n">
         <v>0.4657</v>
@@ -1624,13 +1624,13 @@
         <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3171</v>
+        <v>0.3083</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6458</v>
+        <v>0.4315</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3288</v>
+        <v>-0.1233</v>
       </c>
       <c r="V15" t="n">
         <v>0.467</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5717</v>
+        <v>0.4228</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4175</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1542</v>
+        <v>-0.1573</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1845</v>
+        <v>1.6937</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8252</v>
+        <v>0.2601</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3592</v>
+        <v>1.4336</v>
       </c>
       <c r="J16" t="n">
-        <v>2.952</v>
+        <v>1.5182</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1683</v>
+        <v>0.2642</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.254</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7675999999999999</v>
+        <v>0.1755</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3431</v>
+        <v>-0.0041</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4245</v>
+        <v>0.1796</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.3299</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0709</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7517</v>
+        <v>0.1024</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3192</v>
+        <v>0.4404</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3538</v>
+        <v>-1.3975</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0352</v>
+        <v>0.0788</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1514</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1866</v>
+        <v>0.6257</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6937</v>
+        <v>2.1845</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2601</v>
+        <v>1.8252</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4336</v>
+        <v>0.3592</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5182</v>
+        <v>2.952</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2642</v>
+        <v>2.1683</v>
       </c>
       <c r="L17" t="n">
-        <v>1.254</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1755</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0041</v>
+        <v>-0.3431</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1796</v>
+        <v>-0.4245</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4162</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0848</v>
+        <v>1.578</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3262</v>
+        <v>0.7873</v>
       </c>
       <c r="U17" t="n">
-        <v>0.411</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3975</v>
+        <v>-0.3538</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7006</v>
+        <v>-0.3791</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5735</v>
+        <v>-1.2521</v>
       </c>
       <c r="F18" t="n">
         <v>0.8729</v>
@@ -1858,10 +1858,10 @@
         <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4815</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0562</v>
+        <v>0.2653</v>
       </c>
       <c r="U18" t="n">
         <v>0.5376</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9477</v>
+        <v>-0.5075</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3367</v>
+        <v>0.0151</v>
       </c>
       <c r="F19" t="n">
-        <v>1.389</v>
+        <v>-0.5225</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2175</v>
+        <v>-1.0061</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6739000000000001</v>
+        <v>-1.0616</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4564</v>
+        <v>0.0555</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5784</v>
+        <v>1.2108</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0576</v>
+        <v>0.7675</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.636</v>
+        <v>0.4433</v>
       </c>
       <c r="M19" t="n">
-        <v>0.796</v>
+        <v>-2.2169</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.8291</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1796</v>
+        <v>-0.3878</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7078</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3229</v>
+        <v>0.1986</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3849</v>
+        <v>0.3543</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.4706</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3853</v>
+        <v>-0.9667</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6279</v>
+        <v>-2.4439</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7574</v>
+        <v>1.4771</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0061</v>
+        <v>0.2175</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0616</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0555</v>
+        <v>-0.4564</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2108</v>
+        <v>-0.5784</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7675</v>
+        <v>0.0576</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4433</v>
+        <v>-0.636</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2169</v>
+        <v>0.796</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8291</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3878</v>
+        <v>0.1796</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3249</v>
+        <v>0.6888</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4443</v>
+        <v>0.2158</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1194</v>
+        <v>0.473</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4706</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6433</v>
+        <v>-1.7695</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.285</v>
+        <v>-2.4993</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6417</v>
+        <v>0.7298</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8956</v>
@@ -2092,13 +2092,13 @@
         <v>2.4974</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0341</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7235</v>
+        <v>0.5091</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3106</v>
+        <v>0.3987</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1168</v>
@@ -2125,37 +2125,37 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>19.4042</v>
+        <v>19.4044</v>
       </c>
       <c r="E22" t="n">
-        <v>9.967700000000001</v>
+        <v>9.967699999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>9.436599999999999</v>
+        <v>9.436500000000002</v>
       </c>
       <c r="G22" t="n">
-        <v>9.940099999999999</v>
+        <v>9.940099999999997</v>
       </c>
       <c r="H22" t="n">
         <v>4.061800000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>5.878100000000002</v>
+        <v>5.8781</v>
       </c>
       <c r="J22" t="n">
         <v>16.2079</v>
       </c>
       <c r="K22" t="n">
-        <v>8.9419</v>
+        <v>8.941899999999999</v>
       </c>
       <c r="L22" t="n">
         <v>7.266100000000002</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.267799999999999</v>
+        <v>-6.2678</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.880100000000001</v>
+        <v>-4.8801</v>
       </c>
       <c r="O22" t="n">
         <v>-1.3879</v>
@@ -2170,13 +2170,13 @@
         <v>13.5277</v>
       </c>
       <c r="S22" t="n">
-        <v>7.936599999999999</v>
+        <v>7.9365</v>
       </c>
       <c r="T22" t="n">
-        <v>3.0889</v>
+        <v>3.0888</v>
       </c>
       <c r="U22" t="n">
-        <v>4.8476</v>
+        <v>4.8477</v>
       </c>
       <c r="V22" t="n">
         <v>3.6086</v>
